--- a/Modules/MiX/MiX_BOM.xlsx
+++ b/Modules/MiX/MiX_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\MiX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6585BFC5-25FD-48E9-94D1-7BEFD410F65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D122A190-79E6-4917-9FFB-8B477BE6146B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -197,15 +197,9 @@
     <t>Jack Nut</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/black-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Thonk Trimmer Topper</t>
   </si>
   <si>
@@ -485,6 +479,12 @@
       </rPr>
       <t>***</t>
     </r>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57164621578504</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
   </si>
 </sst>
 </file>
@@ -1396,7 +1396,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1419,7 +1419,7 @@
         <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1430,7 +1430,7 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -1439,7 +1439,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>35</v>
@@ -1453,16 +1453,16 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>35</v>
@@ -1476,19 +1476,19 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1499,19 +1499,19 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -1531,10 +1531,10 @@
         <v>21</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1554,7 +1554,7 @@
         <v>17</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>36</v>
@@ -1577,10 +1577,10 @@
         <v>22</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1594,7 +1594,7 @@
         <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
         <v>32</v>
@@ -1608,13 +1608,13 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
         <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
         <v>30</v>
@@ -1623,7 +1623,7 @@
         <v>38</v>
       </c>
       <c r="J11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1637,16 +1637,16 @@
         <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1666,10 +1666,10 @@
         <v>26</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1686,10 +1686,10 @@
         <v>41</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="J15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1697,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
         <v>40</v>
@@ -1706,10 +1706,10 @@
         <v>41</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="J16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1720,21 +1720,21 @@
         <v>39</v>
       </c>
       <c r="C17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E17" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="J17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1744,12 +1744,12 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1763,14 +1763,14 @@
     <hyperlink ref="F10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
     <hyperlink ref="F11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
     <hyperlink ref="F17" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="F15" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="F16" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="F12:F13" r:id="rId12" display="https://www.tme.eu/hr/en/details/zl211-40kg-s/pin-headers/connfly/ds1022-1-40ruf11/" xr:uid="{6760E9F4-7D95-497E-ABB2-013CB1CCBB26}"/>
-    <hyperlink ref="F12" r:id="rId13" xr:uid="{1FB83572-1784-4F2A-9795-1BC9CAF4A4A8}"/>
-    <hyperlink ref="F13" r:id="rId14" xr:uid="{1384F5B0-07F0-42FD-8E11-D4B5B9168241}"/>
-    <hyperlink ref="F3" r:id="rId15" xr:uid="{CD62976F-E6F0-4843-9662-6335290D56F3}"/>
-    <hyperlink ref="F4" r:id="rId16" xr:uid="{3A7278F6-79B6-483B-92E2-DD4E7AB4FCD1}"/>
-    <hyperlink ref="F8" r:id="rId17" xr:uid="{8A0A8944-6272-4522-A668-7910352C3729}"/>
+    <hyperlink ref="F12:F13" r:id="rId10" display="https://www.tme.eu/hr/en/details/zl211-40kg-s/pin-headers/connfly/ds1022-1-40ruf11/" xr:uid="{6760E9F4-7D95-497E-ABB2-013CB1CCBB26}"/>
+    <hyperlink ref="F12" r:id="rId11" xr:uid="{1FB83572-1784-4F2A-9795-1BC9CAF4A4A8}"/>
+    <hyperlink ref="F13" r:id="rId12" xr:uid="{1384F5B0-07F0-42FD-8E11-D4B5B9168241}"/>
+    <hyperlink ref="F3" r:id="rId13" xr:uid="{CD62976F-E6F0-4843-9662-6335290D56F3}"/>
+    <hyperlink ref="F4" r:id="rId14" xr:uid="{3A7278F6-79B6-483B-92E2-DD4E7AB4FCD1}"/>
+    <hyperlink ref="F8" r:id="rId15" xr:uid="{8A0A8944-6272-4522-A668-7910352C3729}"/>
+    <hyperlink ref="F15" r:id="rId16" xr:uid="{1A964C89-E26C-4630-AC9D-C9F20D6C6CC2}"/>
+    <hyperlink ref="F16" r:id="rId17" xr:uid="{EA04D9D3-F412-4F6B-86E7-E394D557AAB6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId18"/>
